--- a/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Aurélien sent le pain chaud. Papa appelle. C'est l'heure de manger. Aurélien va à la table. Il pose les fesses sur la chaise. Il est assis. Maman s'assoit près de lui. Papa s'assoit aussi. Ils sont ensemble. Le yaourt est frais. Aurélien mange assis. La cuillère cliquette. Maman dit : on mange ensemble, à table. Aurélien reste assis. Il croque le pain. Papa verse l'eau. Aurélien attend, assis. Ils mangent ensemble à table.</t>
+          <t>C'est le matin. Aurélien sent le pain chaud. Papa appelle. C'est l'heure de manger. Aurélien va à la table. Il pose les fesses sur la chaise. Il est assis. Maman s'assoit près de lui. Papa s'assoit aussi. Ils sont ensemble. Le yaourt est frais. Aurélien mange assis. La cuillère cliquette. On mange ensemble, à table. Aurélien reste assis. Il croque le pain. Papa verse l'eau. Aurélien attend, assis. Ils mangent ensemble à table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Aurélien sent le pain chaud. Papa appelle. C'est l'heure de manger. Aurélien va à la table. Il pose les fesses sur la chaise. Il est assis. Maman s'assoit près de lui. Papa s'assoit aussi. Ils sont ensemble. Le yaourt est frais. Aurélien mange assis. La cuillère cliquette.
+maman|On mange ensemble, à table.
+narrateur|Aurélien reste assis. Il croque le pain. Papa verse l'eau. Aurélien attend, assis. Ils mangent ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Aurélien va manger. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Aurélien est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Aurélien boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Aurélien reste assis. Il croque le pain. Papa verse l'eau. Aurélien attend, assis. Ils mangent ensemble à table.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Aurélien va manger. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Aurélien est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Aurélien boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aurélien s'assoit pour le petit-déjeuner</t>
+          <t>Le pain qui saute</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le pain saute. Hop. Le miel brille. Les pantoufles d'Aniss font flap. Il s'assoit. On déjeune ensemble, à table.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Aurélien sent le pain chaud. Papa appelle. C'est l'heure de manger. Aurélien va à la table. Il pose les fesses sur la chaise. Il est assis. Maman s'assoit près de lui. Papa s'assoit aussi. Ils sont ensemble. Le yaourt est frais. Aurélien mange assis. La cuillère cliquette. On mange ensemble, à table. Aurélien reste assis. Il croque le pain. Papa verse l'eau. Aurélien attend, assis. Ils mangent ensemble à table.</t>
+          <t>Le pain saute dans la cuisine. Il fait un petit bruit. Hop. Un rayon touche le pot de miel. Le pot est un peu collant, lui aussi. Une goutte tombe, tout doucement. Les pantoufles d'Aniss sont trop grandes. Elles font flap, flap. Aniss vit ici, avec papa et maman. La maison sent le pain chaud. Dehors, le village est encore calme. Un oiseau chante sur le toit. Aniss, le pain est prêt ! J'arrive, papa ! Aniss marche vers la cuisine. Des miettes dorées attendent sur la planche. Le pain a sauté ! Oui. Hop, dans l'assiette. Viens t'asseoir. Aniss va vers sa chaise. Il tire un peu la chaise. Il s'assoit. Il pose les pieds par terre. Bravo, Aniss. Tu es bien assis. Maman s'assoit près de lui. Papa s'assoit aussi. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Il pose les mains. Le yaourt est frais. Il a un petit chapeau blanc. La cuillère cliquette. Tu as entendu la cuillère ? Elle chante. On attend un petit moment. Aniss tient sa cuillère. Il reste assis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1329,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Aurélien sent le pain chaud. Papa appelle. C'est l'heure de manger. Aurélien va à la table. Il pose les fesses sur la chaise. Il est assis. Maman s'assoit près de lui. Papa s'assoit aussi. Ils sont ensemble. Le yaourt est frais. Aurélien mange assis. La cuillère cliquette.
-maman|On mange ensemble, à table.
-narrateur|Aurélien reste assis. Il croque le pain. Papa verse l'eau. Aurélien attend, assis. Ils mangent ensemble à table.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le pain saute dans la cuisine.
+narrateur|Il fait un petit bruit.
+narrateur|Hop.
+narrateur|Un rayon touche le pot de miel.
+narrateur|Le pot est un peu collant, lui aussi.
+narrateur|Une goutte tombe, tout doucement.
+narrateur|Les pantoufles d'Aniss sont trop grandes.
+narrateur|Elles font flap, flap.
+narrateur|Aniss vit ici, avec papa et maman.
+narrateur|La maison sent le pain chaud.
+narrateur|Dehors, le village est encore calme.
+narrateur|Un oiseau chante sur le toit.
+papa|Aniss, le pain est prêt !
+enfant-m|J'arrive, papa !
+narrateur|Aniss marche vers la cuisine.
+narrateur|Des miettes dorées attendent sur la planche.
+enfant-m|Le pain a sauté !
+papa|Oui.
+papa|Hop, dans l'assiette.
+maman|Viens t'asseoir.
+narrateur|Aniss va vers sa chaise.
+narrateur|Il tire un peu la chaise.
+narrateur|Il s'assoit.
+narrateur|Il pose les pieds par terre.
+maman|Bravo, Aniss.
+maman|Tu es bien assis.
+narrateur|Maman s'assoit près de lui.
+narrateur|Papa s'assoit aussi.
+papa|On est ensemble.
+papa|On mange à table.
+narrateur|Sa chaise ne bouge plus.
+maman|Tu poses les mains sur la table ?
+narrateur|Il pose les mains.
+narrateur|Le yaourt est frais.
+narrateur|Il a un petit chapeau blanc.
+narrateur|La cuillère cliquette.
+papa|Tu as entendu la cuillère ?
+enfant-m|Elle chante.
+maman|On attend un petit moment.
+narrateur|Aniss tient sa cuillère.
+narrateur|Il reste assis.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pain,chaise</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aurélien va manger. Que fait-il ?</t>
+          <t>Aniss va manger. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1557,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Aurélien va manger. Que fait-il ?</t>
+          <t>narrateur|Aniss va manger.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aurélien est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+          <t>Aniss est assis. Il est à table. On est tous assis. On est ensemble. Le yaourt attend. Ta chaise reste à table ? Oui. Aniss reste assis. Une miette dorée brille encore. Tu restes avec nous ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1730,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aurélien est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+          <t>narrateur|Aniss est assis.
+narrateur|Il est à table.
+papa|On est tous assis.
+maman|On est ensemble.
+narrateur|Le yaourt attend.
+papa|Ta chaise reste à table ?
+enfant-m|Oui.
+narrateur|Aniss reste assis.
+narrateur|Une miette dorée brille encore.
+papa|Tu restes avec nous ?
+enfant-m|Oui.
+maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aurélien boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit papa.</t>
+          <t>Papa verse un peu d'eau. L'eau fait un petit bruit. Tu croques le pain ? Aniss croque le pain. C'est croustillant. C'est bon. Tu restes assis. Bravo, Aniss. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Aniss. Ils mangent ensemble. Aniss reste assis. Encore une petite cuillère ? Encore une cuillère de yaourt. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Aniss. Il boit une gorgée. Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1909,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Aurélien boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit papa.</t>
+          <t>narrateur|Papa verse un peu d'eau.
+narrateur|L'eau fait un petit bruit.
+maman|Tu croques le pain ?
+narrateur|Aniss croque le pain.
+enfant-m|C'est croustillant.
+enfant-m|C'est bon.
+papa|Tu restes assis.
+maman|Bravo, Aniss.
+maman|Tu as goûté.
+maman|C'est du bon travail.
+papa|Bon appétit.
+maman|Bon appétit, Aniss.
+narrateur|Ils mangent ensemble.
+narrateur|Aniss reste assis.
+papa|Encore une petite cuillère ?
+narrateur|Encore une cuillère de yaourt.
+papa|Tu restes assis. Bravo.
+enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Merci, Aniss.
+narrateur|Il boit une gorgée.
+narrateur|Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les miettes dorées se reposent. Le miel ne brille plus autant. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2098,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Les miettes dorées se reposent.
+narrateur|Le miel ne brille plus autant.
+papa|On a mangé assis, ensemble.
+enfant-m|C'était bon.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est le matin. Aurélien sent le pain chaud. Papa appelle. C'est l'heure de manger. Aurélien va à la table. Il pose les fesses sur la chaise. Il est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Maman s'assoit près de lui. Papa s'assoit aussi. Ils sont ensemble. Le yaourt est frais. Aurélien mange assis. La cuillère cliquette. Maman dit : on mange ensemble, à table. Aurélien reste assis. Il croque le pain. Papa verse l'eau. Aurélien attend, assis. Ils mangent ensemble à table.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pain saute dans la cuisine. Il fait un petit bruit. Hop. Un rayon touche le pot de miel. Le pot est un peu collant, lui aussi. Une goutte tombe, tout doucement. Les pantoufles d'Aniss sont trop grandes. Elles font flap, flap. Aniss vit ici, avec papa et maman. La maison sent le pain chaud. Dehors, le village est encore calme. Un oiseau chante sur le toit. Aniss, le pain est prêt ! J'arrive, papa ! Aniss marche vers la cuisine. Des miettes dorées attendent sur la planche. Le pain a sauté ! Oui. Hop, dans l'assiette. Viens t'asseoir. Aniss va vers sa chaise. Il tire un peu la chaise. Il s'assoit. Il pose les pieds par terre. Bravo, Aniss. Tu es bien assis. Maman s'assoit près de lui. Papa s'assoit aussi. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Il pose les mains. Le yaourt est frais. Il a un petit chapeau blanc. La cuillère cliquette. Tu as entendu la cuillère ? Elle chante. On attend un petit moment. Aniss tient sa cuillère. Il reste assis.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Aurélien va manger. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss va manger. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1561,7 +1561,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1591,7 +1590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Aurélien est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss est assis. Il est à table. On est tous assis. On est ensemble. Le yaourt attend. Ta chaise reste à table ? Oui. Aniss reste assis. Une miette dorée brille encore. Tu restes avec nous ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1744,7 +1743,6 @@
 maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1769,12 +1767,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa verse un peu d'eau. L'eau fait un petit bruit. Tu croques le pain ? Aniss croque le pain. C'est croustillant. C'est bon. Tu restes assis. Bravo, Aniss. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Aniss. Ils mangent ensemble. Aniss reste assis. Encore une petite cuillère ? Encore une cuillère de yaourt. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Aniss. Il boit une gorgée. Il reste assis jusqu'à la fin.</t>
+          <t>Papa verse un peu d'eau. L'eau fait un petit bruit. Tu croques le pain ? Aniss croque le pain. C'est croustillant. C'est bon. Tu restes assis. Bravo, Aniss. Tu as goûté. Bon appétit. Bon appétit, Aniss. Ils mangent ensemble. Aniss reste assis. Encore une petite cuillère ? Encore une cuillère de yaourt. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Aniss. Il boit une gorgée. Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Aurélien boit une gorgée. Il reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt; jusqu'à la fin. Merci, dit papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa verse un peu d'eau. L'eau fait un petit bruit. Tu croques le pain ? Aniss croque le pain. C'est croustillant. C'est bon. Tu restes assis. Bravo, Aniss. Tu as goûté. Bon appétit. Bon appétit, Aniss. Ils mangent ensemble. Aniss reste assis. Encore une petite cuillère ? Encore une cuillère de yaourt. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Aniss. Il boit une gorgée. Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1918,7 +1916,6 @@
 papa|Tu restes assis.
 maman|Bravo, Aniss.
 maman|Tu as goûté.
-maman|C'est du bon travail.
 papa|Bon appétit.
 maman|Bon appétit, Aniss.
 narrateur|Ils mangent ensemble.
@@ -1933,7 +1930,6 @@
 narrateur|Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1958,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les miettes dorées se reposent. Le miel ne brille plus autant. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>Les miettes dorées se reposent. Le miel ne brille plus autant. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les miettes dorées se reposent. Le miel ne brille plus autant. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,12 +2098,9 @@
 narrateur|Le miel ne brille plus autant.
 papa|On a mangé assis, ensemble.
 enfant-m|C'était bon.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2126,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-05.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aurélien, papa, maman</t>
+          <t>Aniss, papa, maman</t>
         </is>
       </c>
     </row>
